--- a/becpg-plm/becpg-plm-core/src/main/resources/beCPG/birt/exportsearch/product/fr/ExportSuppliers.xlsx
+++ b/becpg-plm/becpg-plm-core/src/main/resources/beCPG/birt/exportsearch/product/fr/ExportSuppliers.xlsx
@@ -261,7 +261,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF006600"/>
+        <fgColor rgb="FF004254"/>
         <bgColor rgb="FF003300"/>
       </patternFill>
     </fill>
@@ -315,12 +315,12 @@
     </xf>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="false"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3" customBuiltin="false"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6" customBuiltin="false"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4" customBuiltin="false"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7" customBuiltin="false"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5" customBuiltin="false"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -333,7 +333,7 @@
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF006600"/>
+      <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
@@ -372,7 +372,7 @@
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF004254"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
@@ -398,19 +398,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.23828125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="24.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="24.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="7" style="0" width="20.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="14" style="0" width="15.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="19" style="0" width="8.23"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
@@ -509,24 +508,23 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.2109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="2" style="0" width="20.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="15" style="0" width="11.2"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
@@ -625,25 +623,24 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.13671875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="12.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="2" style="0" width="19.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="20.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="12" style="0" width="10.12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
